--- a/workbooks/mutants/M07_supplier_rebate.xlsx
+++ b/workbooks/mutants/M07_supplier_rebate.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R93cb242ef8e84938"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RebateCalc" sheetId="2" r:id="R7e92385072e44b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="3" r:id="R7dd9cddba9fd4c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R4a290eb22a7d47a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RebateCalc" sheetId="2" r:id="R1782352362ad46c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TierSchedule" sheetId="3" r:id="R91db6213521745db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="4" r:id="R960d4d527d624065"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,15 +16,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
     <x:numFmt numFmtId="202" formatCode="0.0%;[Red](0.0%);-"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
     <x:numFmt numFmtId="204" formatCode="0.0%"/>
     <x:numFmt numFmtId="205" formatCode="0.00x"/>
+    <x:numFmt numFmtId="206" formatCode="$#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -76,6 +78,12 @@
     <x:font>
       <x:sz val="11"/>
       <x:color rgb="FF475569"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -133,7 +141,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="13">
+  <x:borders count="18">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -225,11 +233,69 @@
         <x:color rgb="FFAAB6C7"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="60">
+  <x:cellXfs count="75">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -319,13 +385,30 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="206" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="206" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="206" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
@@ -805,7 +888,7 @@
         <x:v>SLA multiplier</x:v>
       </x:c>
       <x:c r="Q5" s="34" t="str">
-        <x:v>Tenure multiplier</x:v>
+        <x:v>Effective proration</x:v>
       </x:c>
       <x:c r="R5" s="34" t="str">
         <x:v>Adjusted rebate</x:v>
@@ -860,7 +943,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="N6" s="50" t="n">
-        <x:f>IF(L6&lt;100000,0,IF(L6&lt;250000,0.02,IF(L6&lt;500000,0.03,0.04)))</x:f>
+        <x:f>LOOKUP(L6,TierSchedule!A5:A8,TierSchedule!B5:B8)</x:f>
         <x:v>0.03</x:v>
       </x:c>
       <x:c r="O6" s="48" t="n">
@@ -872,7 +955,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q6" s="51" t="n">
-        <x:f>IF(M6&lt;90,0.5,1)</x:f>
+        <x:f>MIN(1,M6/MAX(1,C6-B6+1))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="R6" s="48" t="n">
@@ -943,6 +1026,108 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="56" t="str">
+        <x:v>Controlled ordered tier lookup</x:v>
+      </x:c>
+      <x:c r="B1" s="56"/>
+      <x:c r="C1" s="56"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="56"/>
+      <x:c r="B2" s="56"/>
+      <x:c r="C2" s="56"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="23" t="str">
+        <x:v>Lower bound (inclusive)</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="str">
+        <x:v>Rate</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="str">
+        <x:v>Upper-bound behavior</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="64" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B5" s="67" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="58" t="str">
+        <x:v>below 100,000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="65" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="B6" s="68" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="C6" s="61" t="str">
+        <x:v>below 250,000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="65" t="n">
+        <x:v>250000</x:v>
+      </x:c>
+      <x:c r="B7" s="68" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="C7" s="61" t="str">
+        <x:v>below 500,000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="66" t="n">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="B8" s="69" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="C8" s="63" t="str">
+        <x:v>no upper bound</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="54" t="str">
+        <x:v>RebateCalc!N6 uses Excel LOOKUP against A5:B8. M03–M05 shift a narrow interval at each inclusive lower bound.</x:v>
+      </x:c>
+      <x:c r="B10" s="54"/>
+      <x:c r="C10" s="54"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="54"/>
+      <x:c r="B11" s="54"/>
+      <x:c r="C11" s="54"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="54"/>
+      <x:c r="B12" s="54"/>
+      <x:c r="C12" s="54"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C2"/>
+    <x:mergeCell ref="A10:C12"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
@@ -952,22 +1137,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="55" t="str">
+      <x:c r="A1" s="70" t="str">
         <x:v>Model Controls</x:v>
       </x:c>
-      <x:c r="B1" s="55"/>
-      <x:c r="C1" s="55"/>
-      <x:c r="D1" s="55"/>
-      <x:c r="E1" s="55"/>
-      <x:c r="F1" s="55"/>
+      <x:c r="B1" s="70"/>
+      <x:c r="C1" s="70"/>
+      <x:c r="D1" s="70"/>
+      <x:c r="E1" s="70"/>
+      <x:c r="F1" s="70"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="55"/>
-      <x:c r="B2" s="55"/>
-      <x:c r="C2" s="55"/>
-      <x:c r="D2" s="55"/>
-      <x:c r="E2" s="55"/>
-      <x:c r="F2" s="55"/>
+      <x:c r="A2" s="70"/>
+      <x:c r="B2" s="70"/>
+      <x:c r="C2" s="70"/>
+      <x:c r="D2" s="70"/>
+      <x:c r="E2" s="70"/>
+      <x:c r="F2" s="70"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
@@ -1082,17 +1267,17 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="56" t="str">
+      <x:c r="A10" s="71" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="B10" s="56"/>
-      <x:c r="C10" s="56"/>
-      <x:c r="D10" s="56"/>
-      <x:c r="E10" s="59" t="str">
+      <x:c r="B10" s="71"/>
+      <x:c r="C10" s="71"/>
+      <x:c r="D10" s="71"/>
+      <x:c r="E10" s="74" t="str">
         <x:f>IF(COUNTIF(E5:E8,"FAIL")=0,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="F10" s="59"/>
+      <x:c r="F10" s="74"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
